--- a/assets/files/apple-financial-model.xlsx
+++ b/assets/files/apple-financial-model.xlsx
@@ -10,16 +10,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Ratios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PE Ratio Analysis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PE Ratio Analysis" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Income Statement'!$A$1:$H$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Balance Sheet'!$A$1:$F$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cash Flow Statement'!$A$1:$I$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Key Ratios'!$A$1:$F$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'DCF Model'!$A$1:$H$99</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'PE Ratio Analysis'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Valuation Summary'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'DCF Model'!$A$1:$H$99</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'PE Ratio Analysis'!$A$1:$F$48</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -31,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -98,8 +100,20 @@
       <color rgb="FF1F1F1F"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -128,6 +142,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF48484A"/>
         <bgColor rgb="FF666699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -272,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -346,6 +370,12 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1373,7 +1403,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
@@ -2258,7 +2288,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
@@ -3237,7 +3267,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
@@ -4141,12 +4171,356 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>Apple Inc. — Multi-Method Valuation Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>All figures USD; per-share in USD. Live price $333.26 (21-Jul-2026), 14,690M diluted shares, net cash $33.1B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>KEY INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Live share price ($)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>333.26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Diluted shares (M)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>14690</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Net cash (cash − debt, $M)</t>
+        </is>
+      </c>
+      <c r="B7" s="14">
+        <f>'DCF Model'!B81-'DCF Model'!B82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FY26E revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B8" s="14">
+        <f>'DCF Model'!D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FY26E EBIT ($M)</t>
+        </is>
+      </c>
+      <c r="B9" s="14">
+        <f>'DCF Model'!D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FY26E D&amp;A ($M)</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>'DCF Model'!D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FY26E EBITDA ($M)</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
+        <f>'DCF Model'!D20+'DCF Model'!D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FY26E EPS ($)</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FY26E Services revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>123350</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FY26E Products revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <f>'DCF Model'!D9-B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="54" t="inlineStr">
+        <is>
+          <t>VALUATION METHODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B17" s="56" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t>Implied value/share ($)</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>vs price</t>
+        </is>
+      </c>
+      <c r="E17" s="56" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DCF (intrinsic, conservative floor)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WACC 9.85%, g 3.5%</t>
+        </is>
+      </c>
+      <c r="C18" s="55">
+        <f>'DCF Model'!B86</f>
+        <v/>
+      </c>
+      <c r="D18" s="57">
+        <f>C18/B5-1</f>
+        <v/>
+      </c>
+      <c r="E18" s="58" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Justified P/E (relative)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>38x × FY26E EPS</t>
+        </is>
+      </c>
+      <c r="C19" s="55">
+        <f>38*B12</f>
+        <v/>
+      </c>
+      <c r="D19" s="57">
+        <f>C19/B5-1</f>
+        <v/>
+      </c>
+      <c r="E19" s="58" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EV/EBITDA (relative)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>28x × FY26E EBITDA</t>
+        </is>
+      </c>
+      <c r="C20" s="55">
+        <f>(28*B11+B7)/B6</f>
+        <v/>
+      </c>
+      <c r="D20" s="57">
+        <f>C20/B5-1</f>
+        <v/>
+      </c>
+      <c r="E20" s="58" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sum-of-the-parts (Services + Products)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Services 13x rev + Products 5.5x rev</t>
+        </is>
+      </c>
+      <c r="C21" s="55">
+        <f>(13*B13+5.5*B14+B7)/B6</f>
+        <v/>
+      </c>
+      <c r="D21" s="57">
+        <f>C21/B5-1</f>
+        <v/>
+      </c>
+      <c r="E21" s="58" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>(Reference) current market multiple</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>40x TTM EPS</t>
+        </is>
+      </c>
+      <c r="C22" s="55">
+        <f>B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>BLENDED VALUATION &amp; RATING</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Blended fair value ($) = Σ weight × method</t>
+        </is>
+      </c>
+      <c r="B25" s="55">
+        <f>SUMPRODUCT(C18:C21,E18:E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Upside / (downside) vs $333.26</t>
+        </is>
+      </c>
+      <c r="B26" s="57">
+        <f>B25/B5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>IF(B26&gt;0.10,"BUY",IF(B26&gt;-0.10,"HOLD","REDUCE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Note: DCF structurally under-prices a 40x quality compounder (Services 26% of revenue at ~75% GM); we weight relative + SOTP methods higher. Even so, every method except a premium P/E sits below spot — no margin of safety. DDM n/a (buyback-led capital return, ~0.4% yield). Street: Buy, median target ~$310 (below spot).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A24:E24"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1D1D1F"/>
@@ -5330,7 +5704,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>4810000</v>
+        <v>4896000</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -5979,7 +6353,7 @@
         </is>
       </c>
       <c r="B85" s="9" t="n">
-        <v>14750</v>
+        <v>14690</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
@@ -6028,7 +6402,7 @@
         </is>
       </c>
       <c r="B88" s="50" t="n">
-        <v>327.44</v>
+        <v>333.26</v>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
@@ -6229,7 +6603,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>Blended target (40% DCF / 30% P/E / 20% EV-EBITDA / 10% peer relative) = $215 -&gt; REDUCE</t>
+          <t>Multi-method blend (see Valuation Summary sheet): DCF $156 / P/E $353 / EV-EBITDA $322 / SOTP $244 -&gt; ~$302, HOLD. DCF alone (~$156) structurally under-prices a 40x quality compounder; do NOT anchor to it.</t>
         </is>
       </c>
       <c r="B99" s="13" t="n"/>
@@ -6255,12 +6629,12 @@
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1D1D1F"/>
@@ -7090,7 +7464,7 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A43:F43"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>